--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:16:18+00:00</t>
+    <t>2025-08-22T11:39:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,10 +261,6 @@
   </si>
   <si>
     <t>*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
-</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1568,47 +1564,47 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1635,29 +1631,29 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1677,10 +1673,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1703,11 +1699,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1758,7 +1754,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1778,10 +1774,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1804,11 +1800,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1859,7 +1855,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1879,39 +1875,39 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1938,29 +1934,29 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1980,39 +1976,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2063,7 +2059,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2083,39 +2079,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2166,7 +2162,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2186,39 +2182,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2227,49 +2223,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2289,17 +2285,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2317,11 +2313,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2372,7 +2368,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2392,10 +2388,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2418,11 +2414,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2473,7 +2469,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2493,10 +2489,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2507,7 +2503,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2519,14 +2515,14 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2548,11 +2544,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2570,7 +2566,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2590,10 +2586,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2604,7 +2600,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2616,7 +2612,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2627,7 +2623,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2645,11 +2641,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2667,7 +2663,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2687,10 +2683,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2713,10 +2709,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2768,7 +2764,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2788,10 +2784,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2814,13 +2810,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2871,7 +2867,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2891,39 +2887,39 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2950,29 +2946,29 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2992,10 +2988,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3020,13 +3016,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3077,7 +3073,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3097,17 +3093,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -3125,11 +3121,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3180,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3200,17 +3196,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -3228,11 +3224,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3283,7 +3279,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3303,17 +3299,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3331,11 +3327,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3386,7 +3382,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3406,17 +3402,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3434,11 +3430,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3489,7 +3485,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3509,10 +3505,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3535,11 +3531,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3590,7 +3586,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3610,10 +3606,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3636,11 +3632,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3691,7 +3687,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3711,39 +3707,39 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3794,7 +3790,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3814,39 +3810,39 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3897,7 +3893,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3917,17 +3913,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3945,13 +3941,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4002,7 +3998,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4022,39 +4018,39 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4081,29 +4077,29 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4123,10 +4119,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4151,11 +4147,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4206,7 +4202,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4226,17 +4222,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -4254,11 +4250,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4309,7 +4305,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4329,17 +4325,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -4357,11 +4353,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4412,7 +4408,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4432,17 +4428,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4460,11 +4456,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4515,7 +4511,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4535,17 +4531,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4563,11 +4559,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4618,7 +4614,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4638,10 +4634,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4664,11 +4660,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4719,7 +4715,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4739,10 +4735,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4765,11 +4761,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4820,7 +4816,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4840,39 +4836,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4923,7 +4919,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4943,17 +4939,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4971,13 +4967,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5028,7 +5024,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5048,17 +5044,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5076,11 +5072,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5131,7 +5127,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5151,10 +5147,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5177,10 +5173,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5232,7 +5228,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5252,39 +5248,39 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5311,29 +5307,29 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5349,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5379,11 +5375,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5434,7 +5430,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5454,10 +5450,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5480,16 +5476,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5511,29 +5507,29 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5553,41 +5549,41 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="F42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
+      <c r="L42" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5638,7 +5634,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5658,39 +5654,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5741,7 +5737,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5761,39 +5757,39 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5844,7 +5840,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5864,41 +5860,41 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5949,7 +5945,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5969,10 +5965,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5995,10 +5991,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6050,7 +6046,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6070,39 +6066,39 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6129,29 +6125,29 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6171,10 +6167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6197,11 +6193,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6252,7 +6248,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6272,10 +6268,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6298,11 +6294,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6353,7 +6349,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6373,39 +6369,39 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6432,29 +6428,29 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6474,39 +6470,39 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6557,7 +6553,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6577,39 +6573,39 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6660,7 +6656,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6680,39 +6676,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6721,49 +6717,49 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6783,17 +6779,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>75</v>
@@ -6811,11 +6807,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6866,7 +6862,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6886,10 +6882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6912,11 +6908,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6967,7 +6963,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6987,10 +6983,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7013,10 +7009,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7029,7 +7025,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7044,29 +7040,29 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7086,10 +7082,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7112,10 +7108,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -7167,7 +7163,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7187,10 +7183,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7213,10 +7209,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -7268,7 +7264,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7288,10 +7284,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7314,10 +7310,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7369,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7389,39 +7385,39 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7448,29 +7444,29 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7490,10 +7486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7516,11 +7512,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7571,7 +7567,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7591,10 +7587,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7617,11 +7613,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7672,7 +7668,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7692,39 +7688,39 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7751,29 +7747,29 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7793,39 +7789,39 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7876,7 +7872,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7896,39 +7892,39 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7979,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7999,39 +7995,39 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8040,49 +8036,49 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8102,17 +8098,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8130,11 +8126,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8185,7 +8181,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8205,10 +8201,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8231,11 +8227,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8286,7 +8282,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8306,10 +8302,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8320,7 +8316,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8332,7 +8328,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8343,7 +8339,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>74</v>
@@ -8361,29 +8357,29 @@
         <v>74</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8403,10 +8399,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8429,10 +8425,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -8484,7 +8480,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8504,39 +8500,39 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8563,29 +8559,29 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8605,39 +8601,39 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8688,7 +8684,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8708,39 +8704,39 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8791,7 +8787,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8811,41 +8807,41 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L74" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8896,7 +8892,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8916,41 +8912,41 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9001,7 +8997,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9021,10 +9017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9047,7 +9043,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9100,7 +9096,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9120,10 +9116,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9146,10 +9142,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9177,29 +9173,29 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9219,39 +9215,39 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9278,29 +9274,29 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9320,10 +9316,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9348,11 +9344,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9403,7 +9399,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9423,17 +9419,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
@@ -9451,11 +9447,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9506,7 +9502,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9526,17 +9522,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9554,11 +9550,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9609,7 +9605,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9629,17 +9625,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9657,11 +9653,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9712,7 +9708,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9732,17 +9728,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
@@ -9760,11 +9756,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9815,7 +9811,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9835,10 +9831,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9861,11 +9857,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9916,7 +9912,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9936,10 +9932,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9962,11 +9958,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10017,7 +10013,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10037,39 +10033,39 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E86" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10120,7 +10116,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10140,39 +10136,39 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10223,7 +10219,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10243,17 +10239,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
@@ -10271,11 +10267,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10326,7 +10322,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10346,10 +10342,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10372,10 +10368,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10427,7 +10423,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10447,10 +10443,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10473,10 +10469,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10528,7 +10524,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10548,10 +10544,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10574,10 +10570,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -10629,7 +10625,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10675,10 +10671,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -10730,7 +10726,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10750,10 +10746,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10776,7 +10772,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10829,7 +10825,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10849,10 +10845,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10875,7 +10871,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10928,7 +10924,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:39:32+00:00</t>
+    <t>2025-08-22T13:00:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T13:00:58+00:00</t>
+    <t>2025-08-22T15:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,6 +261,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
+</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1564,25 +1568,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1600,11 +1604,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1631,11 +1635,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1653,7 +1657,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1673,10 +1677,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1699,11 +1703,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1754,7 +1758,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1774,10 +1778,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1800,11 +1804,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1855,7 +1859,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1875,17 +1879,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>80</v>
@@ -1903,11 +1907,11 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1934,11 +1938,11 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1956,7 +1960,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1976,17 +1980,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -2004,11 +2008,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2059,7 +2063,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2079,17 +2083,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -2107,11 +2111,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2162,7 +2166,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2182,17 +2186,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -2210,11 +2214,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2223,7 +2227,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -2265,7 +2269,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2285,17 +2289,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2313,11 +2317,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2368,7 +2372,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2388,10 +2392,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2414,11 +2418,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2469,7 +2473,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2489,10 +2493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2503,7 +2507,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2515,14 +2519,14 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2544,11 +2548,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2566,7 +2570,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2586,10 +2590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2600,7 +2604,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2612,7 +2616,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2623,7 +2627,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2641,11 +2645,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2663,7 +2667,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2683,10 +2687,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2709,10 +2713,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2764,7 +2768,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2784,10 +2788,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2810,13 +2814,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2867,7 +2871,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2887,17 +2891,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
@@ -2915,11 +2919,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2946,11 +2950,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2968,7 +2972,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2988,10 +2992,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3016,13 +3020,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3073,7 +3077,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3093,17 +3097,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -3121,11 +3125,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3176,7 +3180,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3196,17 +3200,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -3224,11 +3228,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3279,7 +3283,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3299,17 +3303,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3327,11 +3331,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3382,7 +3386,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3402,17 +3406,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3430,11 +3434,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3485,7 +3489,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3505,10 +3509,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3531,11 +3535,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3586,7 +3590,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3606,10 +3610,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3632,11 +3636,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3687,7 +3691,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3707,17 +3711,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3735,11 +3739,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3790,7 +3794,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3810,17 +3814,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3838,11 +3842,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3893,7 +3897,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3913,17 +3917,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3941,13 +3945,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3998,7 +4002,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4018,17 +4022,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -4046,11 +4050,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4077,11 +4081,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4099,7 +4103,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4119,10 +4123,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4147,11 +4151,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4202,7 +4206,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4222,17 +4226,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -4250,11 +4254,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4305,7 +4309,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4325,17 +4329,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -4353,11 +4357,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4408,7 +4412,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4428,17 +4432,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4456,11 +4460,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4511,7 +4515,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4531,17 +4535,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4559,11 +4563,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4614,7 +4618,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4634,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4660,11 +4664,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4715,7 +4719,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4735,10 +4739,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4761,11 +4765,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4816,7 +4820,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4836,17 +4840,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
@@ -4864,11 +4868,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4919,7 +4923,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4939,17 +4943,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4967,13 +4971,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5024,7 +5028,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5044,17 +5048,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5072,11 +5076,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5127,7 +5131,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5147,10 +5151,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5173,10 +5177,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5228,7 +5232,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5248,17 +5252,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5276,11 +5280,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5307,11 +5311,11 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5329,7 +5333,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5349,10 +5353,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5375,11 +5379,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5430,7 +5434,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5450,10 +5454,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5476,16 +5480,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5507,11 +5511,11 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5529,7 +5533,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5549,17 +5553,17 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>75</v>
@@ -5577,13 +5581,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5634,7 +5638,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5654,17 +5658,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5682,11 +5686,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5737,7 +5741,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5757,17 +5761,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5785,11 +5789,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5840,7 +5844,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5860,17 +5864,17 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5888,13 +5892,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5945,7 +5949,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5965,10 +5969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5991,10 +5995,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6046,7 +6050,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6066,17 +6070,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
@@ -6094,11 +6098,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6125,11 +6129,11 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6147,7 +6151,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6167,10 +6171,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6193,11 +6197,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6248,7 +6252,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6268,10 +6272,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6294,11 +6298,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6349,7 +6353,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6369,17 +6373,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6397,11 +6401,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6428,11 +6432,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6450,7 +6454,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6470,17 +6474,17 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6498,11 +6502,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6553,7 +6557,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6573,17 +6577,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6601,11 +6605,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6656,7 +6660,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6676,17 +6680,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>75</v>
@@ -6704,11 +6708,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6717,7 +6721,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6759,7 +6763,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6779,17 +6783,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>75</v>
@@ -6807,11 +6811,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6862,7 +6866,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6882,10 +6886,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6908,11 +6912,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6963,7 +6967,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6983,10 +6987,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7009,10 +7013,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7025,7 +7029,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7040,11 +7044,11 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7062,7 +7066,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7082,10 +7086,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7108,10 +7112,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -7163,7 +7167,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7183,10 +7187,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7209,10 +7213,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -7264,7 +7268,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7284,10 +7288,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7310,10 +7314,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7365,7 +7369,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7385,17 +7389,17 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
@@ -7413,11 +7417,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7444,11 +7448,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7466,7 +7470,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7486,10 +7490,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7512,11 +7516,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7567,7 +7571,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7587,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7613,11 +7617,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7668,7 +7672,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7688,17 +7692,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
@@ -7716,11 +7720,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7747,11 +7751,11 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7769,7 +7773,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7789,17 +7793,17 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -7817,11 +7821,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7872,7 +7876,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7892,17 +7896,17 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -7920,11 +7924,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7975,7 +7979,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7995,17 +7999,17 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>75</v>
@@ -8023,11 +8027,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8036,7 +8040,7 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>74</v>
@@ -8078,7 +8082,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8098,17 +8102,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8126,11 +8130,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8181,7 +8185,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8201,10 +8205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8227,11 +8231,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8282,7 +8286,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8302,10 +8306,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8316,7 +8320,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8328,7 +8332,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8339,7 +8343,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>74</v>
@@ -8357,11 +8361,11 @@
         <v>74</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8379,7 +8383,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8399,10 +8403,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8425,10 +8429,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -8480,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8500,17 +8504,17 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
@@ -8528,11 +8532,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8559,11 +8563,11 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8581,7 +8585,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8601,17 +8605,17 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
@@ -8629,11 +8633,11 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8684,7 +8688,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8704,17 +8708,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -8732,11 +8736,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8787,7 +8791,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8807,17 +8811,17 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>75</v>
@@ -8835,13 +8839,13 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8892,7 +8896,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8912,17 +8916,17 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>75</v>
@@ -8940,13 +8944,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -8997,7 +9001,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9017,10 +9021,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9043,7 +9047,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9096,7 +9100,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9116,10 +9120,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9142,10 +9146,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9173,11 +9177,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9195,7 +9199,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9215,17 +9219,17 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
@@ -9243,11 +9247,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9274,11 +9278,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9296,7 +9300,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9344,11 +9348,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9399,7 +9403,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9419,17 +9423,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
@@ -9447,11 +9451,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9502,7 +9506,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9522,17 +9526,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9550,11 +9554,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9605,7 +9609,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9625,17 +9629,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9653,11 +9657,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9708,7 +9712,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9728,17 +9732,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
@@ -9756,11 +9760,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9811,7 +9815,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9831,10 +9835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9857,11 +9861,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9912,7 +9916,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9932,10 +9936,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9958,11 +9962,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10013,7 +10017,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10033,17 +10037,17 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
@@ -10061,11 +10065,11 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10116,7 +10120,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10136,17 +10140,17 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
@@ -10164,11 +10168,11 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10219,7 +10223,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10239,17 +10243,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
@@ -10267,11 +10271,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10322,7 +10326,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10342,10 +10346,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10368,10 +10372,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10423,7 +10427,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10443,10 +10447,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10469,10 +10473,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10524,7 +10528,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10544,10 +10548,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10570,10 +10574,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -10625,7 +10629,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10671,10 +10675,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -10726,7 +10730,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10746,10 +10750,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10772,7 +10776,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10825,7 +10829,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10845,10 +10849,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10871,7 +10875,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10924,7 +10928,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T15:38:31+00:00</t>
+    <t>2025-08-22T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,10 +261,6 @@
   </si>
   <si>
     <t>*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
-</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1568,47 +1564,47 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1635,29 +1631,29 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1677,10 +1673,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1703,11 +1699,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1758,7 +1754,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1778,10 +1774,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1804,11 +1800,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1859,7 +1855,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1879,39 +1875,39 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1938,29 +1934,29 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1980,39 +1976,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2063,7 +2059,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2083,39 +2079,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2166,7 +2162,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2186,39 +2182,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2227,49 +2223,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2289,17 +2285,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2317,11 +2313,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2372,7 +2368,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2392,10 +2388,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2418,11 +2414,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2473,7 +2469,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2493,10 +2489,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2507,7 +2503,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2519,14 +2515,14 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2548,11 +2544,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2570,7 +2566,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2590,10 +2586,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2604,7 +2600,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2616,7 +2612,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2627,7 +2623,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2645,11 +2641,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2667,7 +2663,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2687,10 +2683,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2713,10 +2709,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2768,7 +2764,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2788,10 +2784,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2814,13 +2810,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2871,7 +2867,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2891,39 +2887,39 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2950,29 +2946,29 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2992,10 +2988,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3020,13 +3016,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3077,7 +3073,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3097,17 +3093,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -3125,11 +3121,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3180,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3200,17 +3196,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -3228,11 +3224,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3283,7 +3279,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3303,17 +3299,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3331,11 +3327,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3386,7 +3382,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3406,17 +3402,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3434,11 +3430,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3489,7 +3485,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3509,10 +3505,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3535,11 +3531,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3590,7 +3586,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3610,10 +3606,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3636,11 +3632,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3691,7 +3687,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3711,39 +3707,39 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3794,7 +3790,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3814,39 +3810,39 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3897,7 +3893,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3917,17 +3913,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3945,13 +3941,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4002,7 +3998,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4022,39 +4018,39 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4081,29 +4077,29 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4123,10 +4119,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4151,11 +4147,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4206,7 +4202,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4226,17 +4222,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -4254,11 +4250,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4309,7 +4305,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4329,17 +4325,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -4357,11 +4353,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4412,7 +4408,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4432,17 +4428,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4460,11 +4456,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4515,7 +4511,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4535,17 +4531,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4563,11 +4559,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4618,7 +4614,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4638,10 +4634,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4664,11 +4660,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4719,7 +4715,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4739,10 +4735,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4765,11 +4761,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4820,7 +4816,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4840,39 +4836,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4923,7 +4919,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4943,17 +4939,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4971,13 +4967,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5028,7 +5024,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5048,17 +5044,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5076,11 +5072,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5131,7 +5127,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5151,10 +5147,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5177,10 +5173,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5232,7 +5228,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5252,39 +5248,39 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5311,29 +5307,29 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5349,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5379,11 +5375,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5434,7 +5430,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5454,10 +5450,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5480,16 +5476,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5511,29 +5507,29 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5553,41 +5549,41 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="F42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
+      <c r="L42" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5638,7 +5634,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5658,39 +5654,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5741,7 +5737,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5761,39 +5757,39 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5844,7 +5840,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5864,41 +5860,41 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5949,7 +5945,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5969,10 +5965,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5995,10 +5991,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6050,7 +6046,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6070,39 +6066,39 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6129,29 +6125,29 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6171,10 +6167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6197,11 +6193,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6252,7 +6248,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6272,10 +6268,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6298,11 +6294,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6353,7 +6349,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6373,39 +6369,39 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6432,29 +6428,29 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6474,39 +6470,39 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6557,7 +6553,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6577,39 +6573,39 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6660,7 +6656,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6680,39 +6676,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6721,49 +6717,49 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6783,17 +6779,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>75</v>
@@ -6811,11 +6807,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6866,7 +6862,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6886,10 +6882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6912,11 +6908,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6967,7 +6963,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6987,10 +6983,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7013,10 +7009,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7029,7 +7025,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7044,29 +7040,29 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7086,10 +7082,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7112,10 +7108,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -7167,7 +7163,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7187,10 +7183,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7213,10 +7209,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -7268,7 +7264,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7288,10 +7284,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7314,10 +7310,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7369,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7389,39 +7385,39 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7448,29 +7444,29 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7490,10 +7486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7516,11 +7512,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7571,7 +7567,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7591,10 +7587,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7617,11 +7613,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7672,7 +7668,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7692,39 +7688,39 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7751,29 +7747,29 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7793,39 +7789,39 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7876,7 +7872,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7896,39 +7892,39 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7979,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7999,39 +7995,39 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8040,49 +8036,49 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8102,17 +8098,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8130,11 +8126,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8185,7 +8181,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8205,10 +8201,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8231,11 +8227,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8286,7 +8282,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8306,10 +8302,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8320,7 +8316,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8332,7 +8328,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8343,7 +8339,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>74</v>
@@ -8361,29 +8357,29 @@
         <v>74</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8403,10 +8399,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8429,10 +8425,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -8484,7 +8480,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8504,39 +8500,39 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K71" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8563,29 +8559,29 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8605,39 +8601,39 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8688,7 +8684,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8708,39 +8704,39 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8791,7 +8787,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8811,41 +8807,41 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="F74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="L74" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8896,7 +8892,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8916,41 +8912,41 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9001,7 +8997,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9021,10 +9017,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9047,7 +9043,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9100,7 +9096,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9120,10 +9116,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9146,10 +9142,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9177,29 +9173,29 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9219,39 +9215,39 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9278,29 +9274,29 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9320,10 +9316,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9348,11 +9344,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9403,7 +9399,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9423,17 +9419,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
@@ -9451,11 +9447,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9506,7 +9502,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9526,17 +9522,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9554,11 +9550,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9609,7 +9605,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9629,17 +9625,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9657,11 +9653,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9712,7 +9708,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9732,17 +9728,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
@@ -9760,11 +9756,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9815,7 +9811,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9835,10 +9831,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9861,11 +9857,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9916,7 +9912,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9936,10 +9932,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9962,11 +9958,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10017,7 +10013,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10037,39 +10033,39 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E86" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10120,7 +10116,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10140,39 +10136,39 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10223,7 +10219,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10243,17 +10239,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
@@ -10271,11 +10267,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10326,7 +10322,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10346,10 +10342,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10372,10 +10368,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10427,7 +10423,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10447,10 +10443,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10473,10 +10469,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10528,7 +10524,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10548,10 +10544,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10574,10 +10570,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -10629,7 +10625,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10675,10 +10671,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -10730,7 +10726,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10750,10 +10746,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10776,7 +10772,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10829,7 +10825,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10849,10 +10845,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10875,7 +10871,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10928,7 +10924,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T16:16:41+00:00</t>
+    <t>2025-08-25T07:57:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T07:57:03+00:00</t>
+    <t>2025-08-25T14:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
